--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GIH2LP</t>
+          <t>GIH2D4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och analysera samhällsutvecklingen relaterat till friluf…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för judons historia och värdegrund samt kunna applicera och…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GIH2WU</t>
+          <t>GIH2D5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för fysiologiska förmågors tränings…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för generell teknik i tävlingsgodkända lyft i disciplinerna…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GIH2XY</t>
+          <t>GIH2D6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten:     - ha förmågan att utifrån en datamängd förklara och visualisera en variabels centr…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:    - nervsystemets och musklernas up…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GIH35W</t>
+          <t>GIH2D7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:    - sammanställa kunskapsläget, utifrån relevant fors…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna redogöra för:    - nervsystemets och musklernas up…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GIH37R</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - reflektera över och diskutera tränarrollen u…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GIH37S</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - reflektera kring och diskutera tränarrollen…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GIH392</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:     - diskutera och problematisera skolämnet idrott och hälsa utifrån olika did…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för krafter, hävarmar och vridande…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GIH394</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - identifiera och redogöra för olika vetenskapliga områden inom idrotts- och…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för krafter, hävarmar och vridande…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GIH3AN</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för rörelseapparatens uppbyggnad oc…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GIH3AP</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för rörelseapparatens uppbyggnad oc…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - hantera mätutrustning och olika metoder för rörelse- och prestationsa…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH2LP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och analysera samhällsutvecklingen relaterat till friluf…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IH1082</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten ska efter genomförd kurs kunna:         - redogöra för idrottsjournalistikens utveckling    - visa förståelse…</t>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:     - visa förmåga att planera, leda och utvärdera träning som skapar fö…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BKE223</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KEA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.  Efter avslutad kurs…</t>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:     - visa förmåga att planera, leda och utvärdera träning som skapar fö…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AMC2BG</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska den studerande självständigt kunna:    - redogöra för farmakokinetik, farmakodynamik samt identif…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdena tränings- och täv…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.    Efte…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdena tränings- och täv…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>NV1024</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa olika teorier om motoriskt lärande och kontroll inom judoträ…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>NV1027</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.    Efter…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa olika teorier om motoriskt lärande och kontroll inom träning…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna    - redogöra på ett fördjupat sätt för centrala be…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:     - tillämpa olika teorier om motoriskt lärande och kontroll inom klättr…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdena tränings- och täv…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse   Efter avslutad kurs ska den studerande kunna:    - visa fördjupade kunskaper om samhälleliga li…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa förmåga att planera, leda och utvärdera träning som skapar förut…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande självständigt kunna:    - visa fördjupad kunskap om olika…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för rörelseapparatens funktionella anatomi samt biomekani…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ASA28A</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för kroppens sensoriska organ samt nervsystemets och musk…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:    - psykologi som…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - planera och genomföra träning vars syfte är att utveckla människans a…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa kunskaper om nationell och internationel…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för olika vetenskapliga förhållningssätt inom forskning   -…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avvikande introfras: unskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa teoretiska och praktiska kunskaper om arb…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för människans energi- och näringsbehov   - redogöra för och…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:      - visa fördjupade kunskaper om olika former…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kunskap om förebyggandet av potentiella idrottsrelaterade skador…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - på grundläggande nivå redogöra för olika vete…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - identifiera, redogöra för och diskutera etiska frågeställningar in…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**    Efter avslutad kurs ska den studerande kunna:      - redogöra för olika socialpolitiska mo…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för fysiologiska förmågors tränings…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>GIH2WU</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:       - visa kunskap om och förståelse för hu…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en grundläggande nivå kunna:    - redogöra för fysiologiska förmågors tränings…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WU</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:    - visa fördjupade och vidgade kunskaper om…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - identifiera och redogöra för olika vetenskapliga områden inom idrotts- och…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:     - diskutera och problematisera skolämnet idrott och hälsa utifrån olika did…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunn…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SA1032</t>
+          <t>GIH2XY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för socialarbetarprogrammets idé om verksamhetsförlagd utbil…</t>
+          <t>Avvikande introfras: Efter godkänd kurs ska studenten:     - ha förmågan att utifrån en datamängd förklara och visualisera en variabels centr…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:       - på en grundläggande nivå redogöra för ol…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på en fördjupad nivå kunna:       - sammanställa kunskapsläget, utifrån relevant…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>GIH35W</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_  Efter avslutad kurs ska den studerande kunna:    - visa fördjupade kunskaper om nationell och…</t>
+          <t>Avvikande introfras: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:    - sammanställa kunskapsläget, utifrån relevant fors…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35W</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASR25T</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - applicera och anpassa evidensbaserad kunskap om global sexuell och re…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ASR25U</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera principer som ligger till grund för rättssäkerhet och…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ASR25V</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:    - genomföra en vetenskaplig undersökning med relevant des…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ASR296</t>
+          <t>GIH37R</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ASR29S</t>
+          <t>GIH37S</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna    - kritiskt reflektera över och analysera begrepp, teorier och pe…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ASR29V</t>
+          <t>GIH392</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten på en fördjupad nivå kunna:    - kritiskt reflektera över begrepp, teorier och hållbarh…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:     - diskutera och problematisera skolämnet idrott och hälsa utifrån olika did…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH392</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ASR2CH</t>
+          <t>GIH394</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna:    - genomföra en vetenskaplig undersökning med relevant design, m…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - identifiera och redogöra för olika vetenskapliga områden inom idrotts- och…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH394</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde.…</t>
+          <t>Avvikande introfras: Efter godkänd kurs ska studenten på en grundläggande nivå kunna:    - reflektera över och diskutera tränarrollen utifrån…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>GIH3AN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.   ### Delkurser  1…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>GIH3AP</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,44 +1810,4148 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.  ### Delkurser  1.…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>GIH3D4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GIH3D5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och diskutera idrottsvetenskap med fokus på träningslära…</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GIH3D6</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för människans energi- och näringsbehov   - redogöra för och…</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GIH3GA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs ska den studerande på en fördjupad nivå kunna:    - utifrån ett valt syfte, designa och genomföra en…</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>IH1001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi I, 7,5 hög…</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>IH1002</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen består av fyra delkurser med mål enligt nedanstående.  ### Delkurser  1.Motorik, anatomi och fysiologi II, 7,5 hö…</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>IH1003</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - redogöra för, samt analysera hur olika faktorer påverkar barns och u…</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>IH1004</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - redogöra för, samt analysera hur livsvillkor och fritidsvanor påverk…</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>IH1005</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel…</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>IH1006</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kunskaper om rörelse som erfarenhet, upplevelse och aktivitet ur…</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>IH1007</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - reflektera kring och analysera dansen som kunskapsområde,    - till…</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>IH1008</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:          - använda och värdera ett brett spektrum av mätmetoder för att an…</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>IH1009</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna         - visa goda kunskaper om** **barns och ungdomars motoriska och pe…</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>IH1010</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna         - visa färdigheter i friluftsteknik och friluftssäkerhet i olika…</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>IH1011</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - påvisa och argumentera för rörelsens och naturens betydelse för bar…</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>IH1012</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna         - redogöra för och analysera utövandet av idrott och friluftsliv i…</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>IH1015</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för grunderna i socialpsykologiska teorier, vad gäller in…</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>IH1020</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>IH1023</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - använda ett brett spektrum av mätmetoder för att analysera, styr…</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>IH1024</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - använda och värdera ett brett spektrum av mätmetoder för evaluer…</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>IH1025</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - använda ett brett spektrum av mätmetoder för att analysera, styr…</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>IH1026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - reflektera över förebyggande, omhändertagande och rehabilitering…</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>IH1029</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: ### Delkurser  1.Idrott och hälsa - ett ämne för alla?, 15 högskolepoäng  Efter avslutad delkurs skall den studerande ku…</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>IH1062</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>IH1082</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Studenten ska efter genomförd kurs kunna:         - redogöra för idrottsjournalistikens utveckling    - visa förståelse…</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>IH1095</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna         - visa förmåga att använda olika metoder för att utvärdera en affär…</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>IH1096</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - upprätta en affärsmodell.…</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>IH1097</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa hur nätverk och partnerskap kan byggas.…</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>IH1098</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa förmåga att identifiera och föreslå lösningar på ett markna…</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>IH1099</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - redogöra för metoder för bedömning av en affärsidés finansiering…</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>IH1100</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa förmåga att kritiskt diskutera affärsetiska frågor utifrån…</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>IH1101</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - redogöra för hur en produktutvecklingsprocess kan planeras och k…</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>IH1102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa förmåga att tillämpa en produktutvecklingsmodell som stöd f…</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>IH1111</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Studenten ska efter genomförd kurs kunna:         - redogöra för idrottsjournalistikens utveckling    - visa förståelse…</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>IH1113</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - tillämpa grundläggande kunskaper inom ämnesområdet fysisk träning med…</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>IH1114</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för de viktigaste mikro- och makronutrienterna och deras bet…</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>IH1122</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna       - definiera begreppet sportmedia     - analysera relationen mellan sa…</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>IH1130</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för kroppens sensoriska organ samt nervsystemets och musk…</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>IH2001</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - uppvisa ett kritiskt vetenskapligt förhållningssätt till forskning r…</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>IH2002</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: ### Delkurser  1.Träningslära, 7,5 högskolepoäng  Efter avslutad delkurs skall den studerande kunna    - analysera och v…</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>IH2003</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:         - visa färdigheter i och förtrogenhet med friluftsteknik och fri…</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>IH2004</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - kommunicera och problematisera begreppet och fenomenet hälsa ur oli…</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>IH2005</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna:    - visa färdigheter i rörelse till olika former av musik    - analyser…</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>IH2006</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall den studerande kunna    - analysera och värdera olika idrotts- och motionsaktiviteter ur ett h…</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>IH3007</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - identifiera ett vetenskapsteoretiskt problem samt kunna tillämpa…</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>BKE223</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KEA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.  Efter avslutad kurs…</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>AMC22C</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Den studerande ska efter genomgången kurs självständigt kunna:    - tillämpa och kritiskt reflektera över teorier och mo…</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>AMC243</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - ingående beskriva nociception, smärtmodulering och smärtupplevelse ur…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>AMC24R</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:    - redogöra för etiologi, symtom, fysiologi, patofysiologi…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>AMC25W</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:    - tillämpa och värdera ett personcentrerat förhållningssä…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>AMC265</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      -  redogöra för farmakokinetik, farmakodynamik, biverkningar och inte…</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>AMC2BG</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs ska den studerande självständigt kunna:    - redogöra för farmakokinetik, farmakodynamik samt identif…</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2BG</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GMC22H</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.  E…</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GMC2AH</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - förklara humana cellers grundläggande funktioner och hur celler sa…</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GMC2M2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva människans anatomi och fysiologiska processer avseende: mats…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>MC1072</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.    Efte…</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>MC1077</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>MC1079</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>MC2017</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       -  redogöra för grundläggande medicinska begrepp såsom psykisk sjukd…</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>MC2020</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande på ett professionellt, systematiskt och självständigt sätt och utifrån en helhets…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>MC3027</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:         - redogöra för farmakokinetik, farmakodynamik samt i…</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GNV2KY</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i och om naturvetenskap och teknik rele…</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>NV1024</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>NV1027</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.    Efter…</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>NV1035</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>NV3001</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att kursdeltagaren ska utveckla kunskaper och förhållningssätt som ökar förutsättningarna fö…</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>PS1018</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PSA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva grunderna för stödjande samtal    - redogöra för grunderna i…</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PS1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>ASA24J</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa fördjupad kunskap om och kritiskt gransk…</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ASA24K</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna    - redogöra på ett fördjupat sätt för centrala be…</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ASA24L</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>ASA24M</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>ASA24N</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska uppnå en bredare och djupare kompetens om äldre personer och åldrande utif…</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>ASA266</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse   Efter avslutad kurs ska den studerande kunna:    - visa fördjupade kunskaper om samhälleliga li…</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>ASA26U</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande självständigt kunna:    - visa fördjupad kunskap om olika…</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>ASA27E</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Kunskap och förståelse **    Efter avslutad kurs ska den studerande kunna:      - visa fördjupad kunskap om aktuell na…</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>ASA28A</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik i vård och omsorg utifrån persp…</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GSA24U</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - redogöra för olika teoretiska perspektiv på v…</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GSA24V</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Den studerande ska efter avslutad kurs kunna:    - visa kunskap om och förståelse för samspelet…</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GSA27Y</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna visa grundläggande kunskaper om:    - psykologi som…</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa kunskaper om nationell och internationel…</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: unskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa teoretiska och praktiska kunskaper om arb…</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>GSA2DW</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:      - visa fördjupade kunskaper om olika former…</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E4</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - visa kunskap om och förståelse för hur familj…</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse        Efter avslutad kurs ska den studerande kunna:    - beskriva olika utredningar och handlägg…</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GSA2GZ</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - redogöra för begrepp, idéer, arbetssätt och teoretiska grunder i k…</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NA</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande kunna:    - på grundläggande nivå redogöra för olika vete…</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NC</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse    Efter avslutat moment ska den studera…</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GSA2RE</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Kunskap och förståelse**    Efter avslutad kurs ska den studerande kunna:      - redogöra för olika socialpolitiska mo…</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SD</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:       - visa kunskap om och förståelse för hu…</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SE</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:    - visa fördjupade och vidgade kunskaper om…</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>GSA32Y</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DM</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DS</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunna:…</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FL</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**  Kunskap och förståelse  Efter godkänd modul ska studenten kunn…</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>SA1032</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för socialarbetarprogrammets idé om verksamhetsförlagd utbil…</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SA1037</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>SA1040</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SA1045</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna:       - på en grundläggande nivå redogöra för ol…</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>SA1046</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - beskriva konsekvenser av mäns våld mot kvinnor och barn på individ-…</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SA1048</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>SA3008</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: _Kunskap och förståelse_  Efter avslutad kurs ska den studerande kunna:    - visa fördjupade kunskaper om nationell och…</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>ASR22N</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>ASR24V</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för centrala begrepp inom global sexuell och reproduktiv häl…</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>ASR24W</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - självständigt och systematiskt söka efter relevanta vetenskapliga art…</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>ASR24X</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kunskap om evidensbaserade metoder för implementering av kvalite…</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ASR25P</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid okomplicerad graviditet, förlossning…</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>ASR25Q</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning…</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>ASR25T</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - applicera och anpassa evidensbaserad kunskap om global sexuell och re…</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>ASR25U</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera principer som ligger till grund för rättssäkerhet och…</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>ASR25V</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande självständigt kunna:    - genomföra en vetenskaplig undersökning med relevant des…</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ASR26N</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - säkerställa progressionen från utbildningsplan och kursplaner på kand…</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>ASR26S</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning…</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>ASR284</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ASR285</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>ASR286</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>ASR296</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>ASR29S</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna    - kritiskt reflektera över och analysera begrepp, teorier och pe…</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29S</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>ASR29U</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna:    - i simulerad miljö utföra undersökningar och behandlingar vid…</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>ASR29V</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs ska studenten på en fördjupad nivå kunna:    - kritiskt reflektera över begrepp, teorier och hållbarh…</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29V</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>ASR2CH</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs ska studenten självständigt kunna:    - genomföra en vetenskaplig undersökning med relevant design, m…</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2CH</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>GSR2A5</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna    - redovisa kunskaper för ungdomar och unga vuxnas reproduktiva hälsa i e…</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>GSR2KZ</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva hälsa, jämlikhet och jämställdhet utifrån hållbarhetsmålen 2…</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>SR3001</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>SR3002</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>SR3003</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>SR3004</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>SR3005</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>SR3006</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>SR3007</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>SR3008</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde.…</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>SR3009</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>SR3010</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>SR3011</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>SR3012</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>SR3013</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>SR3014</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
           <t>SR3015</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>SRP</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Avvikande formulering</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
         <is>
           <t>Avvikande introfras: Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>AVV26K</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för historisk utveckling, teoretiska modeller och centrala b…</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>AVV26M</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska den studerande, med tillämpning inom hälso- och sjukvård och socialt arb…</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>VV2001</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>VV2002</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna    - redogöra för gällande regelverk för olika professioner inom kommunal äldreo…</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>VV3003</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - analysera och bedöma relevansen i problemformuleringar inom vårdveten…</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>VV3006</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna         - diskutera och reflektera över barnmorskep…</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>VV3007</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska studenten kunna    - redogöra för och diskutera begreppen normal gr…</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>VV3009</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:    - kommunicera, diskutera och försvara vetenskap…</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>VV3010</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>VV3011</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap…</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>VV3014</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>VV3015</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E52"/>
+  <autoFilter ref="A1:E204"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1951,6 +6055,310 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$204</definedName>

--- a/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens lärandemål.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Frasningskonsistens lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$204</definedName>
